--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484281_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484281_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0813</v>
+        <v>3.2369</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7151</v>
+        <v>4.8162</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6338</v>
+        <v>-1.5793</v>
       </c>
       <c r="G2" t="n">
         <v>4.0865</v>
@@ -610,13 +610,13 @@
         <v>0.3907</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0518</v>
+        <v>0.1038</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2751</v>
+        <v>-0.1739</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2233</v>
+        <v>0.2778</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4998</v>
+        <v>2.4882</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6673</v>
+        <v>2.4651</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1675</v>
+        <v>0.0231</v>
       </c>
       <c r="G3" t="n">
         <v>1.7981</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5057</v>
+        <v>-0.5173</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0025</v>
+        <v>-0.2047</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5032</v>
+        <v>-0.3125</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9414</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3702</v>
+        <v>2.0392</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3109</v>
+        <v>1.8165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0592</v>
+        <v>0.2226</v>
       </c>
       <c r="G4" t="n">
         <v>1.8411</v>
@@ -766,13 +766,13 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.975</v>
+        <v>-0.3061</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6052</v>
+        <v>-0.0997</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3698</v>
+        <v>-0.2064</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8535</v>
+        <v>-0.8923</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5835</v>
+        <v>-0.7857</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.27</v>
+        <v>-0.1066</v>
       </c>
       <c r="G5" t="n">
         <v>0.06279999999999999</v>
@@ -844,13 +844,13 @@
         <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0726</v>
+        <v>-0.1114</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2037</v>
+        <v>0.0015</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2763</v>
+        <v>-0.1129</v>
       </c>
       <c r="V5" t="n">
         <v>0.719</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.589</v>
+        <v>-2.1082</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2536</v>
+        <v>-1.8952</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3354</v>
+        <v>-0.2131</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4145</v>
+        <v>0.3321</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3684</v>
+        <v>1.5733</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7829</v>
+        <v>-1.2412</v>
       </c>
       <c r="J6" t="n">
-        <v>0.41</v>
+        <v>0.9015</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2481</v>
+        <v>2.0069</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1619</v>
+        <v>-1.1054</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8245</v>
+        <v>-0.5694</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1203</v>
+        <v>-0.4336</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9447</v>
+        <v>-0.1358</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7581</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1929</v>
+        <v>-0.659</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0126</v>
+        <v>-0.4758</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1803</v>
+        <v>-0.1831</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5944</v>
+        <v>-2.7792</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2996</v>
+        <v>-1.0625</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2948</v>
+        <v>-1.7167</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3321</v>
+        <v>-0.4145</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5733</v>
+        <v>0.3684</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2412</v>
+        <v>-0.7829</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9015</v>
+        <v>0.41</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0069</v>
+        <v>0.2481</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1054</v>
+        <v>0.1619</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5694</v>
+        <v>-0.8245</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4336</v>
+        <v>0.1203</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1358</v>
+        <v>-0.9447</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1451</v>
+        <v>0.0027</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8803</v>
+        <v>0.2037</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2648</v>
+        <v>-0.201</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6034</v>
+        <v>-3.5179</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3532</v>
+        <v>-4.0499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7499</v>
+        <v>0.532</v>
       </c>
       <c r="G8" t="n">
         <v>0.1975</v>
@@ -1078,13 +1078,13 @@
         <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4838</v>
+        <v>-0.3983</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7509</v>
+        <v>-0.4476</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2671</v>
+        <v>0.0492</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3869</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0556</v>
+        <v>-3.9078</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1494</v>
+        <v>-1.9471</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9062</v>
+        <v>-1.9607</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4505</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6637</v>
+        <v>-0.5159</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5172</v>
+        <v>-0.3149</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1465</v>
+        <v>-0.201</v>
       </c>
       <c r="V9" t="n">
         <v>-2.16</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0602</v>
+        <v>-4.3635</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8135</v>
+        <v>-2.1169</v>
       </c>
       <c r="F10" t="n">
         <v>-2.2466</v>
@@ -1234,10 +1234,10 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3631</v>
+        <v>-0.6665</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1515</v>
+        <v>-0.1518</v>
       </c>
       <c r="U10" t="n">
         <v>-0.5147</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.8048</v>
+        <v>-9.804599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7595</v>
+        <v>-2.759499999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.045199999999999</v>
+        <v>-7.0453</v>
       </c>
       <c r="G11" t="n">
         <v>3.998</v>
@@ -1312,10 +1312,10 @@
         <v>10.7439</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.0679</v>
+        <v>-3.068</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6634</v>
+        <v>-1.6632</v>
       </c>
       <c r="U11" t="n">
         <v>-1.4046</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9543</v>
+        <v>7.3934</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0282</v>
+        <v>6.9136</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9261</v>
+        <v>0.4798</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7348</v>
+        <v>2.4979</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6933</v>
+        <v>1.6071</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9585</v>
+        <v>0.8908</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1503</v>
+        <v>4.6908</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0289</v>
+        <v>2.3152</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1214</v>
+        <v>2.3756</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4156</v>
+        <v>-2.1929</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6644</v>
+        <v>-0.7081</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0799</v>
+        <v>-1.4848</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1609</v>
+        <v>0.2043</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2768</v>
+        <v>-0.1243</v>
       </c>
       <c r="U12" t="n">
-        <v>0.884</v>
+        <v>0.3286</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>3.3238</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5545</v>
+        <v>3.3238</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9142</v>
+        <v>5.1814</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0036</v>
+        <v>2.4215</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08939999999999999</v>
+        <v>2.7599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4979</v>
+        <v>2.7348</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6071</v>
+        <v>3.6933</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8908</v>
+        <v>-0.9585</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6908</v>
+        <v>3.1503</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3152</v>
+        <v>3.0289</v>
       </c>
       <c r="L13" t="n">
-        <v>2.3756</v>
+        <v>0.1214</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1929</v>
+        <v>-0.4156</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7081</v>
+        <v>0.6644</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4848</v>
+        <v>-1.0799</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2749</v>
+        <v>1.3881</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0343</v>
+        <v>0.6701</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2406</v>
+        <v>0.7179</v>
       </c>
       <c r="V13" t="n">
-        <v>3.3238</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3238</v>
+        <v>0.5545</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9786</v>
+        <v>3.1623</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3483</v>
+        <v>4.8539</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3697</v>
+        <v>-1.6915</v>
       </c>
       <c r="G14" t="n">
         <v>3.118</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5887</v>
+        <v>0.595</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2529</v>
+        <v>0.2526</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3358</v>
+        <v>0.3424</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9414</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3703</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6983</v>
+        <v>0.8187</v>
       </c>
       <c r="F15" t="n">
-        <v>0.672</v>
+        <v>0.0557</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0965</v>
+        <v>-3.8691</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1228</v>
+        <v>-3.0336</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0263</v>
+        <v>-0.8356</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6913</v>
+        <v>-1.3418</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7201</v>
+        <v>-1.856</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9712</v>
+        <v>0.5142</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7878</v>
+        <v>-2.5273</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8429</v>
+        <v>-1.1775</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9449</v>
+        <v>-1.3498</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8575</v>
+        <v>0.7436</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9372</v>
+        <v>0.3875</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9204</v>
+        <v>0.3561</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6093</v>
+        <v>2.4373</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3399</v>
+        <v>0.312</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5265</v>
+        <v>-3.2629</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1867</v>
+        <v>3.5749</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.8691</v>
+        <v>-0.4432</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.0336</v>
+        <v>-0.5646</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8356</v>
+        <v>0.1214</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3418</v>
+        <v>-1.1768</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.856</v>
+        <v>-1.164</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5142</v>
+        <v>-0.0128</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5273</v>
+        <v>0.7336</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1775</v>
+        <v>0.5994</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3498</v>
+        <v>0.1342</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1326</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.0953</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.1137</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.4373</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.7731</v>
-      </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.327</v>
+        <v>0.0453</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.7685</v>
+        <v>-0.5151</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4414</v>
+        <v>0.5603</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4432</v>
+        <v>-0.0965</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5646</v>
+        <v>-0.1228</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1214</v>
+        <v>0.0263</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1768</v>
+        <v>1.6913</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.164</v>
+        <v>0.7201</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0128</v>
+        <v>0.9712</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7336</v>
+        <v>-1.7878</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5994</v>
+        <v>-0.8429</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1342</v>
+        <v>-0.9449</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1926</v>
+        <v>1.5325</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6382</v>
+        <v>0.7238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4456</v>
+        <v>0.8087</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2921</v>
+        <v>-2.4999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6976</v>
+        <v>-2.0825</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5946</v>
+        <v>-0.4174</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7666</v>
+        <v>-5.1732</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0921</v>
+        <v>-1.4915</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6745</v>
+        <v>-3.6818</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0223</v>
+        <v>-2.0316</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0223</v>
+        <v>-0.2392</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.7923</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7443</v>
+        <v>-3.1417</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0698</v>
+        <v>-1.2522</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6745</v>
+        <v>-1.8895</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3611</v>
+        <v>0.1693</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3247</v>
+        <v>-0.2928</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0363</v>
+        <v>0.4621</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2772</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1333</v>
+        <v>-2.6421</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0936</v>
+        <v>-2.102</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0397</v>
+        <v>-0.5401</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.1732</v>
+        <v>-2.7666</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4915</v>
+        <v>-2.0921</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.6818</v>
+        <v>-0.6745</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0316</v>
+        <v>-2.0223</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2392</v>
+        <v>-2.0223</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.7923</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1417</v>
+        <v>-0.7443</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2522</v>
+        <v>-0.0698</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8895</v>
+        <v>-0.6745</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4642</v>
+        <v>0.0111</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.304</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1603</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2772</v>
@@ -1969,31 +1969,31 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>9.804900000000002</v>
+        <v>11.8269</v>
       </c>
       <c r="E20" t="n">
-        <v>7.0452</v>
+        <v>7.045199999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7594</v>
+        <v>4.7816</v>
       </c>
       <c r="G20" t="n">
         <v>-3.9979</v>
       </c>
       <c r="H20" t="n">
-        <v>2.070800000000002</v>
+        <v>2.0708</v>
       </c>
       <c r="I20" t="n">
-        <v>-6.0689</v>
+        <v>-6.068899999999999</v>
       </c>
       <c r="J20" t="n">
         <v>9.014900000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>5.635600000000002</v>
+        <v>5.635600000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>3.379399999999999</v>
+        <v>3.3794</v>
       </c>
       <c r="M20" t="n">
         <v>-13.013</v>
@@ -2014,19 +2014,19 @@
         <v>16.6042</v>
       </c>
       <c r="S20" t="n">
-        <v>3.0681</v>
+        <v>5.0903</v>
       </c>
       <c r="T20" t="n">
         <v>1.4046</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6633</v>
+        <v>3.6856</v>
       </c>
       <c r="V20" t="n">
         <v>4.8746</v>
       </c>
       <c r="W20" t="n">
-        <v>7.369599999999999</v>
+        <v>7.3696</v>
       </c>
       <c r="X20" t="n">
         <v>-2.4949</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484281_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484281_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8923</v>
+        <v>0.914</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7857</v>
+        <v>0.914</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1066</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9599</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0227</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1663</v>
+        <v>0.914</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.857</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0233</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1034</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1028</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1114</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1129</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.719</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.719</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1082</v>
+        <v>-1.8063</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8952</v>
+        <v>-1.6997</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2131</v>
+        <v>-0.1066</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3321</v>
+        <v>-0.8511</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5733</v>
+        <v>-2.2668</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2412</v>
+        <v>1.4157</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9015</v>
+        <v>0.2523</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0069</v>
+        <v>-1.164</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1054</v>
+        <v>1.4163</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5694</v>
+        <v>-1.1034</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4336</v>
+        <v>-1.1028</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1358</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.659</v>
+        <v>-0.1114</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4758</v>
+        <v>0.0015</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1831</v>
+        <v>-0.1129</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6093</v>
+        <v>0.719</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0.719</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7792</v>
+        <v>-2.1082</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0625</v>
+        <v>-1.8952</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7167</v>
+        <v>-0.2131</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4145</v>
+        <v>0.3321</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3684</v>
+        <v>1.5733</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7829</v>
+        <v>-1.2412</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41</v>
+        <v>0.9015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2481</v>
+        <v>2.0069</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>-1.1054</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8245</v>
+        <v>-0.5694</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1203</v>
+        <v>-0.4336</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9447</v>
+        <v>-0.1358</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7581</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0027</v>
+        <v>-0.659</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2037</v>
+        <v>-0.4758</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.201</v>
+        <v>-0.1831</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5179</v>
+        <v>-2.7792</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0499</v>
+        <v>-1.0625</v>
       </c>
       <c r="F8" t="n">
-        <v>0.532</v>
+        <v>-1.7167</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1975</v>
+        <v>-0.4145</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7368</v>
+        <v>0.3684</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5393</v>
+        <v>-0.7829</v>
       </c>
       <c r="J8" t="n">
-        <v>1.391</v>
+        <v>0.41</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9289</v>
+        <v>0.2481</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5379</v>
+        <v>0.1619</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1935</v>
+        <v>-0.8245</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1921</v>
+        <v>0.1203</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0014</v>
+        <v>-0.9447</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.9301</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3983</v>
+        <v>0.0027</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4476</v>
+        <v>0.2037</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0492</v>
+        <v>-0.201</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3869</v>
+        <v>-0.6093</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1097</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9078</v>
+        <v>-3.5179</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9471</v>
+        <v>-4.0499</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9607</v>
+        <v>0.532</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4505</v>
+        <v>0.1975</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0305</v>
+        <v>0.7368</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5799</v>
+        <v>-0.5393</v>
       </c>
       <c r="J9" t="n">
-        <v>0.044</v>
+        <v>1.391</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6716</v>
+        <v>1.9289</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7156</v>
+        <v>-0.5379</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4945</v>
+        <v>-1.1935</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3589</v>
+        <v>-1.1921</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1356</v>
+        <v>-0.0014</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5159</v>
+        <v>-0.3983</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3149</v>
+        <v>-0.4476</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.201</v>
+        <v>0.0492</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.16</v>
+        <v>-0.3869</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>-0.1097</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3635</v>
+        <v>-3.9078</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1169</v>
+        <v>-1.9471</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2466</v>
+        <v>-1.9607</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4551</v>
+        <v>-0.4505</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2814</v>
+        <v>-1.0305</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1737</v>
+        <v>0.5799</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9883</v>
+        <v>0.044</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4899</v>
+        <v>-0.6716</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4984</v>
+        <v>0.7156</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4668</v>
+        <v>-0.4945</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7915</v>
+        <v>-0.3589</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6753</v>
+        <v>-0.1356</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6665</v>
+        <v>-0.5159</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1518</v>
+        <v>-0.3149</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5147</v>
+        <v>-0.201</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>-2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.804599999999999</v>
+        <v>-4.3635</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.759499999999998</v>
+        <v>-2.1169</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.0453</v>
+        <v>-2.2466</v>
       </c>
       <c r="G11" t="n">
-        <v>3.998</v>
+        <v>-3.4551</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0709</v>
+        <v>-2.2814</v>
       </c>
       <c r="I11" t="n">
-        <v>6.068799999999999</v>
+        <v>-1.1737</v>
       </c>
       <c r="J11" t="n">
-        <v>13.0131</v>
+        <v>-0.9883</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5646</v>
+        <v>-0.4899</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4483</v>
+        <v>-0.4984</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.015000000000001</v>
+        <v>-2.4668</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.6355</v>
+        <v>-1.7915</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.3793</v>
+        <v>-0.6753</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.8602</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-16.604</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>10.7439</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.068</v>
+        <v>-0.6665</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6632</v>
+        <v>-0.1518</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4046</v>
+        <v>-0.5147</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.8744</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>2.495</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.369499999999999</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.3934</v>
+        <v>-9.804600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9136</v>
+        <v>-2.759499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4798</v>
+        <v>-7.0453</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4979</v>
+        <v>3.9981</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6071</v>
+        <v>-2.0708</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8908</v>
+        <v>6.0688</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6908</v>
+        <v>13.0131</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3152</v>
+        <v>3.5646</v>
       </c>
       <c r="L12" t="n">
-        <v>2.3756</v>
+        <v>9.4483</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1929</v>
+        <v>-9.015000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7081</v>
+        <v>-5.6355</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4848</v>
+        <v>-3.3793</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3674</v>
+        <v>-5.8602</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-16.604</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3441</v>
+        <v>10.7439</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2043</v>
+        <v>-3.068</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1243</v>
+        <v>-1.6632</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3286</v>
+        <v>-1.4046</v>
       </c>
       <c r="V12" t="n">
-        <v>3.3238</v>
+        <v>-4.8744</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3238</v>
+        <v>2.495</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-7.3695</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1814</v>
+        <v>7.3934</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4215</v>
+        <v>6.9136</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7599</v>
+        <v>0.4798</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7348</v>
+        <v>2.4979</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6933</v>
+        <v>1.6071</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9585</v>
+        <v>0.8908</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1503</v>
+        <v>4.6908</v>
       </c>
       <c r="K13" t="n">
-        <v>3.0289</v>
+        <v>2.3152</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1214</v>
+        <v>2.3756</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4156</v>
+        <v>-2.1929</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6644</v>
+        <v>-0.7081</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0799</v>
+        <v>-1.4848</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3881</v>
+        <v>0.2043</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6701</v>
+        <v>-0.1243</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7179</v>
+        <v>0.3286</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2772</v>
+        <v>3.3238</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5545</v>
+        <v>3.3238</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1623</v>
+        <v>5.1814</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8539</v>
+        <v>2.4215</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6915</v>
+        <v>2.7599</v>
       </c>
       <c r="G14" t="n">
-        <v>3.118</v>
+        <v>2.7348</v>
       </c>
       <c r="H14" t="n">
-        <v>4.075</v>
+        <v>3.6933</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.957</v>
+        <v>-0.9585</v>
       </c>
       <c r="J14" t="n">
-        <v>6.055</v>
+        <v>3.1503</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8529</v>
+        <v>3.0289</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2021</v>
+        <v>0.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.937</v>
+        <v>-0.4156</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7779</v>
+        <v>0.6644</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1591</v>
+        <v>-1.0799</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>0.595</v>
+        <v>1.3881</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2526</v>
+        <v>0.6701</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3424</v>
+        <v>0.7179</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9414</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4996</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.441</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8745000000000001</v>
+        <v>3.1623</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8187</v>
+        <v>4.8539</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0557</v>
+        <v>-1.6915</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.8691</v>
+        <v>3.118</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.0336</v>
+        <v>4.075</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8356</v>
+        <v>-0.957</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.3418</v>
+        <v>6.055</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.856</v>
+        <v>4.8529</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5142</v>
+        <v>1.2021</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5273</v>
+        <v>-2.937</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1775</v>
+        <v>-0.7779</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3498</v>
+        <v>-2.1591</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7436</v>
+        <v>0.595</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3875</v>
+        <v>0.2526</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3561</v>
+        <v>0.3424</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4373</v>
+        <v>-0.9414</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>0.4996</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-1.441</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.312</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.2629</v>
+        <v>0.8187</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5749</v>
+        <v>0.0557</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4432</v>
+        <v>-3.8691</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5646</v>
+        <v>-3.0336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1214</v>
+        <v>-0.8356</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1768</v>
+        <v>-1.3418</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.164</v>
+        <v>-1.856</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0128</v>
+        <v>0.5142</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7336</v>
+        <v>-2.5273</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5994</v>
+        <v>-1.1775</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1342</v>
+        <v>-1.3498</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4464</v>
+        <v>0.7436</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1326</v>
+        <v>0.3875</v>
       </c>
       <c r="U16" t="n">
-        <v>0.579</v>
+        <v>0.3561</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1811,72 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0453</v>
+        <v>0.312</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5151</v>
+        <v>-3.2629</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5603</v>
+        <v>3.5749</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0965</v>
+        <v>-0.4432</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1228</v>
+        <v>-0.5646</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0263</v>
+        <v>0.1214</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6913</v>
+        <v>-1.1768</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7201</v>
+        <v>-1.164</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9712</v>
+        <v>-0.0128</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7878</v>
+        <v>0.7336</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8429</v>
+        <v>0.5994</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9449</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5325</v>
+        <v>0.4464</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7238</v>
+        <v>-0.1326</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8087</v>
+        <v>0.579</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4999</v>
+        <v>0.307</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0825</v>
+        <v>0.307</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4174</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.1732</v>
+        <v>0.307</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4915</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.6818</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0316</v>
+        <v>0.307</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2392</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7923</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1417</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2522</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8895</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1693</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2928</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4621</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6421</v>
+        <v>0.0453</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.102</v>
+        <v>-0.5151</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5401</v>
+        <v>0.5603</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7666</v>
+        <v>-0.0965</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0921</v>
+        <v>-0.1228</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6745</v>
+        <v>0.0263</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.0223</v>
+        <v>1.6913</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0223</v>
+        <v>0.7201</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.9712</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7443</v>
+        <v>-1.7878</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0698</v>
+        <v>-0.8429</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6745</v>
+        <v>-0.9449</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0111</v>
+        <v>1.5325</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.7238</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.8087</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,68 +2060,235 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>11.8269</v>
+        <v>-2.6421</v>
       </c>
       <c r="E20" t="n">
-        <v>7.045199999999999</v>
+        <v>-2.102</v>
       </c>
       <c r="F20" t="n">
+        <v>-0.5401</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-2.7666</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.0921</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.7443</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.0698</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.07969999999999999</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P. MONES RIERA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-2.8068</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.3894</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.4174</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-5.4802</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.7984</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-3.6818</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.3386</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.5462</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.7923</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-3.1417</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.2522</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1.8895</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.2928</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484281_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11.827</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7.045299999999999</v>
+      </c>
+      <c r="F22" t="n">
         <v>4.7816</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G22" t="n">
         <v>-3.9979</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.0708</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-6.068899999999999</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="H22" t="n">
+        <v>2.0709</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-6.0689</v>
+      </c>
+      <c r="J22" t="n">
         <v>9.014900000000001</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K22" t="n">
         <v>5.635600000000001</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L22" t="n">
         <v>3.3794</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M22" t="n">
         <v>-13.013</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N22" t="n">
         <v>-3.5646</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O22" t="n">
         <v>-9.4483</v>
       </c>
-      <c r="P20" t="n">
-        <v>5.8602</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="P22" t="n">
+        <v>5.860199999999999</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-10.7437</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R22" t="n">
         <v>16.6042</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S22" t="n">
         <v>5.0903</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>1.4046</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>3.6856</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V22" t="n">
         <v>4.8746</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W22" t="n">
         <v>7.3696</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X22" t="n">
         <v>-2.4949</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
